--- a/project/outputs_xlsx_solution/simple-branch.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/simple-branch.2-wide.xlsx
@@ -62,15 +62,18 @@
     <t>bne X2, X1, 16</t>
   </si>
   <si>
-    <t>IS/EX</t>
-  </si>
-  <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
     <t>EX</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>addi X2, X2, 10</t>
   </si>
   <si>
@@ -83,13 +86,40 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -504,7 +534,7 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +554,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -550,13 +580,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -567,7 +597,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>5</v>
@@ -579,12 +609,12 @@
         <v>9</v>
       </c>
       <c r="L5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -592,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -600,31 +630,71 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
